--- a/A 题/output/ga_p1_makespan.xlsx
+++ b/A 题/output/ga_p1_makespan.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三层对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三算法对比" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,10 +449,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>7.8827</v>
+        <v>7.8402</v>
       </c>
       <c r="D2" t="n">
-        <v>7.725</v>
+        <v>7.7262</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.068</v>
+        <v>7.0611</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0635</v>
+        <v>7.0608</v>
       </c>
     </row>
     <row r="4">
@@ -481,10 +481,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>8.364599999999999</v>
+        <v>8.342599999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>8.2963</v>
+        <v>8.287599999999999</v>
       </c>
     </row>
     <row r="5">
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.7332</v>
+        <v>7.5553</v>
       </c>
       <c r="D5" t="n">
-        <v>7.6838</v>
+        <v>7.4853</v>
       </c>
     </row>
   </sheetData>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,22 +525,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>第一层GA Tmax(h)</t>
+          <t>簇编码GA+ILS Tmax(h)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>第二层簇编码GA Tmax(h)</t>
+          <t>ACO Tmax(h)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
           <t>OR-Tools参考 Tmax(h)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>第二层改善(h)</t>
         </is>
       </c>
     </row>
@@ -551,17 +546,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.014699999999999</v>
+        <v>7.8402</v>
       </c>
       <c r="C2" t="n">
-        <v>7.8827</v>
+        <v>7.9345</v>
       </c>
       <c r="D2" t="n">
         <v>7.883</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -570,17 +562,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.159</v>
+        <v>7.0611</v>
       </c>
       <c r="C3" t="n">
-        <v>7.068</v>
+        <v>7.0978</v>
       </c>
       <c r="D3" t="n">
         <v>7.178</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.091</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -589,17 +578,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.8286</v>
+        <v>8.342599999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>8.364599999999999</v>
+        <v>8.42</v>
       </c>
       <c r="D4" t="n">
         <v>8.372999999999999</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.464</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -608,16 +594,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.0009</v>
+        <v>7.5553</v>
       </c>
       <c r="C5" t="n">
-        <v>7.7332</v>
+        <v>7.6559</v>
       </c>
       <c r="D5" t="n">
         <v>8.02</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.2677</v>
       </c>
     </row>
   </sheetData>
